--- a/public/static/客户产品价格新建导入.xlsx
+++ b/public/static/客户产品价格新建导入.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="32445" windowHeight="14955"/>
+    <workbookView windowHeight="17775"/>
   </bookViews>
   <sheets>
     <sheet name="客户产品价格" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
   <si>
     <t>序号</t>
   </si>
@@ -139,6 +139,12 @@
   </si>
   <si>
     <t>预负荷</t>
+  </si>
+  <si>
+    <t>角度</t>
+  </si>
+  <si>
+    <t>钢球/中心径/倒角</t>
   </si>
   <si>
     <t>备注</t>
@@ -1398,7 +1404,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:U3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
@@ -1407,11 +1413,11 @@
     <col min="5" max="5" width="20" style="2" customWidth="1"/>
     <col min="6" max="11" width="13.225" customWidth="1"/>
     <col min="12" max="17" width="14.3333333333333" customWidth="1"/>
-    <col min="18" max="18" width="15.4416666666667" customWidth="1"/>
-    <col min="19" max="19" width="29.1083333333333" customWidth="1"/>
+    <col min="18" max="19" width="15.4416666666667" customWidth="1"/>
+    <col min="20" max="21" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:19">
+    <row r="1" ht="25" customHeight="1" spans="1:21">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1469,10 +1475,16 @@
       <c r="S1" s="3" t="s">
         <v>18</v>
       </c>
+      <c r="T1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" s="3" t="s">
+        <v>20</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:19">
+    <row r="2" ht="20" customHeight="1" spans="1:21">
       <c r="A2" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1492,8 +1504,10 @@
       <c r="Q2" s="7"/>
       <c r="R2" s="7"/>
       <c r="S2" s="7"/>
+      <c r="T2" s="7"/>
+      <c r="U2" s="7"/>
     </row>
-    <row r="3" customFormat="1" ht="15" spans="1:19">
+    <row r="3" customFormat="1" ht="15" spans="1:21">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1515,6 +1529,8 @@
       <c r="Q3" s="7"/>
       <c r="R3" s="7"/>
       <c r="S3" s="7"/>
+      <c r="T3" s="7"/>
+      <c r="U3" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1533,7 +1549,7 @@
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>

--- a/public/static/客户产品价格新建导入.xlsx
+++ b/public/static/客户产品价格新建导入.xlsx
@@ -10,7 +10,7 @@
     <sheet name="客户产品价格" sheetId="1" r:id="rId1"/>
     <sheet name="说明" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
   <si>
     <t>序号</t>
   </si>
@@ -97,6 +97,9 @@
       </rPr>
       <t>(必填)</t>
     </r>
+  </si>
+  <si>
+    <t>配对方式</t>
   </si>
   <si>
     <t>单价(含税)</t>
@@ -1404,20 +1407,20 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:V3"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="9.225" customWidth="1"/>
     <col min="2" max="2" width="17.1083333333333" customWidth="1"/>
     <col min="3" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="20" style="2" customWidth="1"/>
-    <col min="6" max="11" width="13.225" customWidth="1"/>
-    <col min="12" max="17" width="14.3333333333333" customWidth="1"/>
-    <col min="18" max="19" width="15.4416666666667" customWidth="1"/>
-    <col min="20" max="21" width="29.1083333333333" customWidth="1"/>
+    <col min="5" max="6" width="20" style="2" customWidth="1"/>
+    <col min="7" max="12" width="13.225" customWidth="1"/>
+    <col min="13" max="18" width="14.3333333333333" customWidth="1"/>
+    <col min="19" max="20" width="15.4416666666667" customWidth="1"/>
+    <col min="21" max="22" width="29.1083333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="25" customHeight="1" spans="1:21">
+    <row r="1" ht="25" customHeight="1" spans="1:22">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -1433,7 +1436,7 @@
       <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="3" t="s">
@@ -1481,10 +1484,13 @@
       <c r="U1" s="3" t="s">
         <v>20</v>
       </c>
+      <c r="V1" s="3" t="s">
+        <v>21</v>
+      </c>
     </row>
-    <row r="2" ht="20" customHeight="1" spans="1:21">
+    <row r="2" ht="20" customHeight="1" spans="1:22">
       <c r="A2" s="6" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="B2" s="7"/>
       <c r="C2" s="7"/>
@@ -1506,8 +1512,9 @@
       <c r="S2" s="7"/>
       <c r="T2" s="7"/>
       <c r="U2" s="7"/>
+      <c r="V2" s="7"/>
     </row>
-    <row r="3" customFormat="1" ht="15" spans="1:21">
+    <row r="3" customFormat="1" ht="15" spans="1:22">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1531,6 +1538,7 @@
       <c r="S3" s="7"/>
       <c r="T3" s="7"/>
       <c r="U3" s="7"/>
+      <c r="V3" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1549,7 +1557,7 @@
   <sheetData>
     <row r="1" ht="96" customHeight="1" spans="1:1">
       <c r="A1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" ht="25" customHeight="1"/>
